--- a/data/trans_dic/P02E$nadie-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa</t>
+          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,91; 95,35</t>
+          <t>84,31; 95,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,42; 91,1</t>
+          <t>80,3; 91,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,97; 91,63</t>
+          <t>80,11; 91,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,0; 93,03</t>
+          <t>85,48; 93,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,04; 92,47</t>
+          <t>86,41; 92,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,24; 93,5</t>
+          <t>84,11; 93,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,49; 92,91</t>
+          <t>86,62; 92,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85,52; 91,07</t>
+          <t>85,52; 90,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84,69; 91,73</t>
+          <t>84,27; 91,62</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,79; 95,39</t>
+          <t>89,85; 95,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,69; 95,46</t>
+          <t>91,87; 95,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,0; 94,83</t>
+          <t>90,31; 94,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90,13; 94,47</t>
+          <t>90,07; 94,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>91,48; 94,74</t>
+          <t>91,49; 94,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,19; 90,98</t>
+          <t>86,39; 91,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,83; 94,28</t>
+          <t>91,01; 94,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>92,09; 94,57</t>
+          <t>92,11; 94,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,66; 92,01</t>
+          <t>88,67; 92,16</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,43; 84,93</t>
+          <t>70,34; 84,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,31; 92,57</t>
+          <t>82,0; 92,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,61; 94,71</t>
+          <t>84,45; 94,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,05; 95,65</t>
+          <t>87,08; 95,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,8; 92,78</t>
+          <t>83,62; 92,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,63; 87,12</t>
+          <t>76,47; 87,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,74; 89,62</t>
+          <t>82,2; 89,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84,53; 91,47</t>
+          <t>85,08; 91,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81,54; 89,47</t>
+          <t>81,24; 89,19</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,2; 92,21</t>
+          <t>86,69; 91,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89,53; 93,19</t>
+          <t>89,48; 93,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,18; 93,15</t>
+          <t>89,18; 93,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89,69; 93,36</t>
+          <t>89,92; 93,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,06; 93,08</t>
+          <t>90,16; 93,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,53; 89,58</t>
+          <t>85,56; 89,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,37; 92,3</t>
+          <t>89,42; 92,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>90,41; 92,67</t>
+          <t>90,53; 92,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87,6; 90,51</t>
+          <t>87,69; 90,49</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa</t>
+          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>96183; 108017</t>
+          <t>95502; 107741</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>145610; 164939</t>
+          <t>145399; 165014</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102001; 116872</t>
+          <t>102178; 117092</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>230453; 252222</t>
+          <t>231754; 253259</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>334013; 358951</t>
+          <t>335420; 359885</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>166737; 185070</t>
+          <t>166485; 185047</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>332496; 357160</t>
+          <t>332967; 356971</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>486837; 518434</t>
+          <t>486838; 517984</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>275661; 298554</t>
+          <t>274288; 298219</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>347209; 368849</t>
+          <t>347435; 369317</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>573115; 596644</t>
+          <t>574201; 597145</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>432101; 455265</t>
+          <t>433568; 455402</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>512257; 536920</t>
+          <t>511894; 536321</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>827794; 857251</t>
+          <t>827868; 858546</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>601148; 634556</t>
+          <t>602494; 635616</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>867457; 900440</t>
+          <t>869206; 901413</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1408834; 1446778</t>
+          <t>1409194; 1448086</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1043956; 1083430</t>
+          <t>1044080; 1085213</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88908; 107217</t>
+          <t>88800; 106920</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>145711; 163890</t>
+          <t>145172; 163762</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122265; 136871</t>
+          <t>122044; 137126</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144803; 159093</t>
+          <t>144845; 159261</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>187591; 207699</t>
+          <t>187202; 207652</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>163659; 186067</t>
+          <t>163312; 187045</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>239162; 262201</t>
+          <t>240483; 262076</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>338884; 366702</t>
+          <t>341088; 367112</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>291981; 320379</t>
+          <t>290910; 319388</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>546033; 577409</t>
+          <t>542866; 575356</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>880169; 916169</t>
+          <t>879692; 916451</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>670768; 700613</t>
+          <t>670770; 700302</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>902148; 938991</t>
+          <t>904399; 938538</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1366090; 1411974</t>
+          <t>1367614; 1410901</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>948471; 993358</t>
+          <t>948866; 992708</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1458464; 1506307</t>
+          <t>1459284; 1507798</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2260191; 2316795</t>
+          <t>2263334; 2315387</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1630247; 1684476</t>
+          <t>1631918; 1684104</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$nadie-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,31; 95,11</t>
+          <t>85,69; 95,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,3; 91,14</t>
+          <t>80,17; 90,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,11; 91,8</t>
+          <t>78,97; 91,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,48; 93,41</t>
+          <t>85,39; 92,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,41; 92,71</t>
+          <t>85,55; 92,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,11; 93,49</t>
+          <t>84,33; 93,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,62; 92,86</t>
+          <t>86,83; 92,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85,52; 90,99</t>
+          <t>85,55; 90,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84,27; 91,62</t>
+          <t>84,33; 91,81</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,85; 95,51</t>
+          <t>89,58; 95,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,87; 95,54</t>
+          <t>91,78; 95,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,31; 94,85</t>
+          <t>90,36; 94,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90,07; 94,37</t>
+          <t>89,89; 94,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>91,49; 94,88</t>
+          <t>91,31; 94,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,39; 91,14</t>
+          <t>86,32; 91,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,01; 94,39</t>
+          <t>90,68; 94,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>92,11; 94,65</t>
+          <t>92,11; 94,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,67; 92,16</t>
+          <t>88,43; 92,03</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,34; 84,7</t>
+          <t>70,37; 84,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,0; 92,5</t>
+          <t>82,07; 92,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,45; 94,89</t>
+          <t>84,8; 94,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,08; 95,75</t>
+          <t>86,46; 95,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,62; 92,76</t>
+          <t>83,94; 93,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,47; 87,58</t>
+          <t>76,19; 87,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,2; 89,58</t>
+          <t>81,4; 89,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85,08; 91,57</t>
+          <t>85,3; 91,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81,24; 89,19</t>
+          <t>81,1; 89,33</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,69; 91,88</t>
+          <t>87,12; 92,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89,48; 93,22</t>
+          <t>89,43; 93,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,18; 93,1</t>
+          <t>89,08; 93,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89,92; 93,31</t>
+          <t>89,79; 93,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,16; 93,01</t>
+          <t>90,09; 92,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,56; 89,52</t>
+          <t>85,68; 89,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,42; 92,39</t>
+          <t>89,36; 92,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>90,53; 92,61</t>
+          <t>90,38; 92,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87,69; 90,49</t>
+          <t>87,66; 90,56</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>95502; 107741</t>
+          <t>97068; 107976</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>145399; 165014</t>
+          <t>145161; 164735</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102178; 117092</t>
+          <t>100732; 116781</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>231754; 253259</t>
+          <t>231514; 251652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>335420; 359885</t>
+          <t>332087; 358613</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>166485; 185047</t>
+          <t>166915; 185440</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>332967; 356971</t>
+          <t>333768; 356850</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>486838; 517984</t>
+          <t>486979; 517934</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>274288; 298219</t>
+          <t>274486; 298817</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>347435; 369317</t>
+          <t>346377; 368695</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>574201; 597145</t>
+          <t>573637; 596290</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>433568; 455402</t>
+          <t>433800; 455484</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>511894; 536321</t>
+          <t>510863; 536433</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>827868; 858546</t>
+          <t>826242; 857795</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>602494; 635616</t>
+          <t>602055; 635907</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>869206; 901413</t>
+          <t>865995; 899030</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1409194; 1448086</t>
+          <t>1409206; 1448808</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1044080; 1085213</t>
+          <t>1041308; 1083671</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88800; 106920</t>
+          <t>88830; 107197</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>145172; 163762</t>
+          <t>145294; 164445</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122044; 137126</t>
+          <t>122544; 137105</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144845; 159261</t>
+          <t>143818; 159207</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>187202; 207652</t>
+          <t>187908; 208304</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>163312; 187045</t>
+          <t>162726; 186968</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>240483; 262076</t>
+          <t>238152; 262564</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>341088; 367112</t>
+          <t>341962; 368100</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>290910; 319388</t>
+          <t>290392; 319864</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>542866; 575356</t>
+          <t>545566; 576200</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>879692; 916451</t>
+          <t>879246; 915628</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>670770; 700302</t>
+          <t>670040; 701710</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>904399; 938538</t>
+          <t>903129; 938878</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1367614; 1410901</t>
+          <t>1366515; 1409518</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>948866; 992708</t>
+          <t>950170; 993894</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1459284; 1507798</t>
+          <t>1458314; 1506480</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2263334; 2315387</t>
+          <t>2259598; 2317032</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1631918; 1684104</t>
+          <t>1631525; 1685487</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$nadie-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
+          <t>Población que no tiene ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
+          <t>Población que no tiene ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
